--- a/Result/profitability/4123.xlsx
+++ b/Result/profitability/4123.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>1.17</v>
       </c>
       <c r="M2" t="n">
-        <v>1.95125</v>
+        <v>0.1812499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>43.83875</v>
+        <v>43.495</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-2.11</v>
       </c>
       <c r="M3" t="n">
-        <v>1.64</v>
+        <v>0.05249999999999994</v>
       </c>
       <c r="N3" t="n">
-        <v>43.86875</v>
+        <v>43.44125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>1.73</v>
       </c>
       <c r="M4" t="n">
-        <v>1.99125</v>
+        <v>0.1737499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>43.2675</v>
+        <v>43.3375</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,13 +1018,13 @@
         <v>0.32</v>
       </c>
       <c r="M5" t="n">
-        <v>1.93625</v>
+        <v>0.3399999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>43.585</v>
+        <v>44.19875</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.33</v>
       </c>
       <c r="M6" t="n">
-        <v>2.10375</v>
+        <v>-0.09375000000000004</v>
       </c>
       <c r="N6" t="n">
-        <v>44.79</v>
+        <v>45.245</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>1.15</v>
       </c>
       <c r="M7" t="n">
-        <v>1.7725</v>
+        <v>-1.07125</v>
       </c>
       <c r="N7" t="n">
-        <v>45.46125</v>
+        <v>45.67375</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.49</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8375</v>
+        <v>-1.2125</v>
       </c>
       <c r="N8" t="n">
-        <v>45.81</v>
+        <v>45.44375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.21</v>
       </c>
       <c r="M9" t="n">
-        <v>0.53625</v>
+        <v>0.5362499999999999</v>
       </c>
       <c r="N9" t="n">
         <v>44.5425</v>
@@ -1645,10 +1645,10 @@
         <v>0.06</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3975</v>
+        <v>0.3974999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>44.33</v>
+        <v>44.33000000000001</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>0.6712499999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>43.38500000000001</v>
+        <v>43.385</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1899,7 +1899,7 @@
         <v>0.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0.45625</v>
+        <v>0.4562499999999999</v>
       </c>
       <c r="N12" t="n">
         <v>43.18625</v>
@@ -2026,7 +2026,7 @@
         <v>0.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4175</v>
+        <v>0.4174999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>42.74375</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4123</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>432</v>
+      </c>
+      <c r="D75" t="n">
+        <v>243</v>
+      </c>
+      <c r="E75" t="n">
+        <v>189</v>
+      </c>
+      <c r="F75" t="n">
+        <v>43.65</v>
+      </c>
+      <c r="G75" t="n">
+        <v>486</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>112.46%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-13449</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-12963</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-10447</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-13.78</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.08250000000000002</v>
+      </c>
+      <c r="N75" t="n">
+        <v>43.43625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-16.4</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-6.259541984732824</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.93</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.06290253327608419</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-12.77</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>12.64356435643564</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.909999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1267423851316467</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
